--- a/docs/templates/question-import-template.xlsx
+++ b/docs/templates/question-import-template.xlsx
@@ -675,8 +675,8 @@
       </c>
       <c r="S3" s="3" t="inlineStr">
         <is>
-          <t>试题文件：解析方案.md
-答案解析文件：来源合规检查.md</t>
+          <t>试题文件：README.md
+答案解析文件：PARSING.md</t>
         </is>
       </c>
     </row>
